--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Next 50 ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Next 50 ETF.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="172">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Nifty Next 50 ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -61,97 +61,163 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Hindustan Aeronautics Ltd.</t>
+  </si>
+  <si>
+    <t>INE066F01020</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Divi's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE361B01024</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>The Indian Hotels Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE053A01029</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Cholamandalam Investment And Finance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE121A01024</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Tata Power Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE245A01021</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>TVS Motor Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE494B01023</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>Varun Beverages Ltd.</t>
+  </si>
+  <si>
+    <t>INE200M01039</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E01011</t>
+  </si>
+  <si>
+    <t>Godrej Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE102D01028</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
   </si>
   <si>
     <t>Retailing</t>
   </si>
   <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Jio Financial Services Ltd</t>
-  </si>
-  <si>
-    <t>INE758E01017</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Hindustan Aeronautics Ltd.</t>
-  </si>
-  <si>
-    <t>INE066F01020</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Varun Beverages Ltd.</t>
-  </si>
-  <si>
-    <t>INE200M01039</t>
-  </si>
-  <si>
-    <t>Beverages</t>
-  </si>
-  <si>
-    <t>Divi's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE361B01024</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>Tata Power Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE245A01021</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E01011</t>
+    <t>Bajaj Holdings &amp; Investment Ltd.</t>
+  </si>
+  <si>
+    <t>INE118A01012</t>
   </si>
   <si>
     <t>Info Edge (India) Ltd.</t>
   </si>
   <si>
-    <t>INE663F01024</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE494B01023</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
+    <t>INE663F01032</t>
+  </si>
+  <si>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>GAIL (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE129A01019</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>DLF Ltd.</t>
+  </si>
+  <si>
+    <t>INE271C01023</t>
+  </si>
+  <si>
+    <t>Realty</t>
   </si>
   <si>
     <t>Rural Electrification Corporation Ltd.</t>
@@ -160,6 +226,15 @@
     <t>INE020B01018</t>
   </si>
   <si>
+    <t>Pidilite Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE318A01026</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
     <t>LTIMindtree Ltd.</t>
   </si>
   <si>
@@ -169,16 +244,127 @@
     <t>It - Software</t>
   </si>
   <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Cholamandalam Investment And Finance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE121A01024</t>
+    <t>Bank Of Baroda</t>
+  </si>
+  <si>
+    <t>INE028A01039</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>United Spirits Ltd.</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
+    <t>ICICI Lombard General Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE765G01017</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>CG Power and Industrial Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE067A01029</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Adani Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE814H01011</t>
+  </si>
+  <si>
+    <t>Macrotech Developers Ltd.</t>
+  </si>
+  <si>
+    <t>INE670K01029</t>
+  </si>
+  <si>
+    <t>Shree Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE070A01015</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A01022</t>
+  </si>
+  <si>
+    <t>Havells India Ltd.</t>
+  </si>
+  <si>
+    <t>INE176B01034</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Ambuja Cements Ltd.</t>
+  </si>
+  <si>
+    <t>INE079A01024</t>
+  </si>
+  <si>
+    <t>Punjab National Bank</t>
+  </si>
+  <si>
+    <t>INE160A01022</t>
+  </si>
+  <si>
+    <t>Jindal Steel &amp; Power Ltd.</t>
+  </si>
+  <si>
+    <t>INE749A01030</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Torrent Pharmaceuticals Ltd.</t>
+  </si>
+  <si>
+    <t>INE685A01028</t>
+  </si>
+  <si>
+    <t>Adani Energy Solutions Ltd.</t>
+  </si>
+  <si>
+    <t>INE931S01010</t>
+  </si>
+  <si>
+    <t>ABB India Ltd.</t>
+  </si>
+  <si>
+    <t>INE117A01022</t>
+  </si>
+  <si>
+    <t>Adani Green Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE364U01010</t>
   </si>
   <si>
     <t>Siemens Ltd.</t>
@@ -187,172 +373,16 @@
     <t>INE003A01024</t>
   </si>
   <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Bajaj Holdings &amp; Investment Ltd.</t>
-  </si>
-  <si>
-    <t>INE118A01012</t>
-  </si>
-  <si>
-    <t>Indian Oil Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE242A01010</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>GAIL (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE129A01019</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>DLF Ltd.</t>
-  </si>
-  <si>
-    <t>INE271C01023</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Pidilite Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE318A01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Godrej Consumer Products Ltd.</t>
-  </si>
-  <si>
-    <t>INE102D01028</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
-    <t>United Spirits Ltd.</t>
-  </si>
-  <si>
-    <t>INE854D01024</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Adani Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE814H01011</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A01039</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Havells India Ltd.</t>
-  </si>
-  <si>
-    <t>INE176B01034</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A01022</t>
-  </si>
-  <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Macrotech Developers Ltd.</t>
-  </si>
-  <si>
-    <t>INE670K01029</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
-  </si>
-  <si>
-    <t>INE476A01022</t>
-  </si>
-  <si>
     <t>Dabur India Ltd.</t>
   </si>
   <si>
     <t>INE016A01026</t>
   </si>
   <si>
-    <t>ABB India Ltd.</t>
-  </si>
-  <si>
-    <t>INE117A01022</t>
-  </si>
-  <si>
-    <t>Torrent Pharmaceuticals Ltd.</t>
-  </si>
-  <si>
-    <t>INE685A01028</t>
-  </si>
-  <si>
-    <t>Adani Green Energy Ltd.</t>
-  </si>
-  <si>
-    <t>INE364U01010</t>
-  </si>
-  <si>
-    <t>Jindal Steel &amp; Power Ltd.</t>
-  </si>
-  <si>
-    <t>INE749A01030</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
+    <t>Bosch Ltd.</t>
+  </si>
+  <si>
+    <t>INE323A01026</t>
   </si>
   <si>
     <t>JSW Energy Ltd</t>
@@ -361,10 +391,10 @@
     <t>INE121E01018</t>
   </si>
   <si>
-    <t>Adani Energy Solutions Ltd.</t>
-  </si>
-  <si>
-    <t>INE931S01010</t>
+    <t>ICICI Prudential Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE726G01019</t>
   </si>
   <si>
     <t>Indian Railway Finance Corporation Ltd.</t>
@@ -373,49 +403,16 @@
     <t>INE053F01010</t>
   </si>
   <si>
-    <t>Bharat Heavy Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE257A01026</t>
-  </si>
-  <si>
-    <t>NHPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE848E01016</t>
-  </si>
-  <si>
-    <t>Bosch Ltd.</t>
-  </si>
-  <si>
-    <t>INE323A01026</t>
-  </si>
-  <si>
-    <t>Indian Railway Catering and Tourism Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE335Y01020</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
     <t>Zydus Lifesciences Ltd.</t>
   </si>
   <si>
     <t>INE010B01027</t>
   </si>
   <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
-  </si>
-  <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A01016</t>
+    <t>Hyundai Motor India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0V6F01027</t>
   </si>
   <si>
     <t>Life Insurance Corporation of India</t>
@@ -424,10 +421,22 @@
     <t>INE0J1Y01017</t>
   </si>
   <si>
-    <t>Adani total gas Ltd.</t>
-  </si>
-  <si>
-    <t>INE399L01023</t>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
+  </si>
+  <si>
+    <t>Swiggy Ltd</t>
+  </si>
+  <si>
+    <t>INE00H001014</t>
+  </si>
+  <si>
+    <t>Bajaj Housing Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE377Y01014</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -484,19 +493,19 @@
     <t>Name of the Instrument</t>
   </si>
   <si>
-    <t>Adani Green Energy Ltd</t>
-  </si>
-  <si>
-    <t>Indian Railway Finance Corporation Limited</t>
-  </si>
-  <si>
-    <t>NHPC Limted</t>
-  </si>
-  <si>
-    <t>Shree Cement Limited</t>
-  </si>
-  <si>
-    <t>Adani Total Gas Ltd</t>
+    <t>AVENUE SUPERMARTS LIMITED</t>
+  </si>
+  <si>
+    <t>INDIAN RAILWAY FINANCE CORPORATION LIMITED</t>
+  </si>
+  <si>
+    <t>MACROTECH DEVELOPERS LTD</t>
+  </si>
+  <si>
+    <t>SHREE CEMENT LIMITED</t>
+  </si>
+  <si>
+    <t>Swiggy Limited</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
@@ -508,7 +517,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -746,7 +755,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -839,9 +848,6 @@
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -938,13 +944,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -962,7 +968,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="21221700"/>
+          <a:off x="666750" y="21031200"/>
           <a:ext cx="3810000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -977,13 +983,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1001,7 +1007,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="24079200"/>
+          <a:off x="666750" y="23888700"/>
           <a:ext cx="3810000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1335,19 +1341,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J123"/>
+  <dimension ref="B1:J122"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="27" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="27" width="57.142857142857146" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="27" width="16.571428571428573" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="27" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="27" width="34.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="27" width="10.857142857142858" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="27" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="27" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="27" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="27" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="26" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="26" width="57.142857142857146" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="26" width="16.571428571428573" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="26" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="26" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="26" width="10.857142857142858" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="26" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="26" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="26" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="26" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1435,10 +1441,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>121099.11</v>
+        <v>151393.26</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9998583141963999</v>
+        <v>0.9992414358607001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1472,10 +1478,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>121099.11</v>
+        <v>151393.26</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9998583141963999</v>
+        <v>0.9992414358607001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1498,13 +1504,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>3706167</v>
+        <v>126943</v>
       </c>
       <c r="G8" s="15">
-        <v>8166.54</v>
+        <v>6766.06</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0674272743807</v>
+        <v>0.0446580482482</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1527,13 +1533,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>104865</v>
+        <v>122946</v>
       </c>
       <c r="G9" s="15">
-        <v>4534.73</v>
+        <v>6115.46</v>
       </c>
       <c r="H9" s="16">
-        <v>0.037441129775</v>
+        <v>0.0403638909114</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1556,13 +1562,13 @@
         <v>23</v>
       </c>
       <c r="F10" s="14">
-        <v>1754112</v>
+        <v>82147</v>
       </c>
       <c r="G10" s="15">
-        <v>4238.81</v>
+        <v>5431.56</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0349978577118</v>
+        <v>0.0358499434742</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1585,13 +1591,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="14">
-        <v>906259</v>
+        <v>1097953</v>
       </c>
       <c r="G11" s="15">
-        <v>4000.23</v>
+        <v>4782.13</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0330280150218</v>
+        <v>0.0315635084922</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1614,13 +1620,13 @@
         <v>29</v>
       </c>
       <c r="F12" s="14">
-        <v>101531</v>
+        <v>568224</v>
       </c>
       <c r="G12" s="15">
-        <v>3997.07</v>
+        <v>4374.47</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0330019243901</v>
+        <v>0.0288728288428</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1643,13 +1649,13 @@
         <v>32</v>
       </c>
       <c r="F13" s="14">
-        <v>716093</v>
+        <v>272395</v>
       </c>
       <c r="G13" s="15">
-        <v>3843.63</v>
+        <v>4361.04</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0317350425796</v>
+        <v>0.0287841867693</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1672,13 +1678,13 @@
         <v>35</v>
       </c>
       <c r="F14" s="14">
-        <v>67887</v>
+        <v>1086464</v>
       </c>
       <c r="G14" s="15">
-        <v>3786.53</v>
+        <v>4267.63</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0312635947734</v>
+        <v>0.0281676524366</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1701,13 +1707,13 @@
         <v>38</v>
       </c>
       <c r="F15" s="14">
-        <v>902440</v>
+        <v>151967</v>
       </c>
       <c r="G15" s="15">
-        <v>3289.39</v>
+        <v>4225.9</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0271589439438</v>
+        <v>0.0278922217793</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1727,16 +1733,16 @@
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F16" s="14">
-        <v>777301</v>
+        <v>76313</v>
       </c>
       <c r="G16" s="15">
-        <v>3284.10</v>
+        <v>4205.23</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0271152669054</v>
+        <v>0.0277557935097</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1747,25 +1753,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F17" s="14">
-        <v>41814</v>
+        <v>868000</v>
       </c>
       <c r="G17" s="15">
-        <v>3229.59</v>
+        <v>4131.25</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0266652035093</v>
+        <v>0.0272675030705</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1776,25 +1782,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F18" s="14">
-        <v>125380</v>
+        <v>1254119</v>
       </c>
       <c r="G18" s="15">
-        <v>3081.72</v>
+        <v>3993.11</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0254443105653</v>
+        <v>0.0263557371705</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1805,25 +1811,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F19" s="14">
-        <v>666805</v>
+        <v>942092</v>
       </c>
       <c r="G19" s="15">
-        <v>2999.62</v>
+        <v>3824.42</v>
       </c>
       <c r="H19" s="16">
-        <v>0.024766449534</v>
+        <v>0.0252423320043</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1834,25 +1840,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F20" s="14">
-        <v>49444</v>
+        <v>309891</v>
       </c>
       <c r="G20" s="15">
-        <v>2924.19</v>
+        <v>3816</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0241436595512</v>
+        <v>0.0251867574504</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1863,25 +1869,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="F21" s="14">
-        <v>79069</v>
+        <v>95173</v>
       </c>
       <c r="G21" s="15">
-        <v>2897.60</v>
+        <v>3808.92</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0239241184449</v>
+        <v>0.0251400273029</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1892,25 +1898,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F22" s="14">
-        <v>223377</v>
+        <v>28052</v>
       </c>
       <c r="G22" s="15">
-        <v>2872.29</v>
+        <v>3762.90</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0237151456958</v>
+        <v>0.0248362813444</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1921,25 +1927,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>57</v>
-      </c>
       <c r="F23" s="14">
-        <v>47202</v>
+        <v>251103</v>
       </c>
       <c r="G23" s="15">
-        <v>2866.74</v>
+        <v>3584.50</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0236693219598</v>
+        <v>0.023658787233</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1950,25 +1956,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F24" s="14">
-        <v>23113</v>
+        <v>2417653</v>
       </c>
       <c r="G24" s="15">
-        <v>2671.79</v>
+        <v>3432.34</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0220597116303</v>
+        <v>0.0226544850805</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1979,25 +1985,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F25" s="14">
-        <v>2002713</v>
+        <v>1745390</v>
       </c>
       <c r="G25" s="15">
-        <v>2573.29</v>
+        <v>3312.75</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0212464435233</v>
+        <v>0.0218651548071</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2008,25 +2014,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F26" s="14">
-        <v>1443735</v>
+        <v>415120</v>
       </c>
       <c r="G26" s="15">
-        <v>2557.14</v>
+        <v>3312.03</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0211131005799</v>
+        <v>0.0218604025887</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2037,25 +2043,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="F27" s="14">
-        <v>342565</v>
+        <v>808147</v>
       </c>
       <c r="G27" s="15">
-        <v>2552.28</v>
+        <v>3251.18</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0210729738489</v>
+        <v>0.021458774132</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2066,25 +2072,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F28" s="14">
-        <v>127712</v>
+        <v>99750</v>
       </c>
       <c r="G28" s="15">
-        <v>2373.53</v>
+        <v>3099.43</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0195971192893</v>
+        <v>0.0204571781039</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2095,25 +2101,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F29" s="14">
-        <v>82182</v>
+        <v>59849</v>
       </c>
       <c r="G29" s="15">
-        <v>2360.02</v>
+        <v>3033.69</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0194855735824</v>
+        <v>0.020023274164</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2124,25 +2130,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F30" s="14">
-        <v>201202</v>
+        <v>1198271</v>
       </c>
       <c r="G30" s="15">
-        <v>2255.98</v>
+        <v>2990.29</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0186265643047</v>
+        <v>0.0197368210001</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2153,25 +2159,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="F31" s="14">
-        <v>157670</v>
+        <v>1907711</v>
       </c>
       <c r="G31" s="15">
-        <v>2245.22</v>
+        <v>2921.09</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0185377240526</v>
+        <v>0.0192800800107</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2182,25 +2188,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="F32" s="14">
-        <v>1575883</v>
+        <v>191080</v>
       </c>
       <c r="G32" s="15">
-        <v>2226.09</v>
+        <v>2904.61</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0183797766528</v>
+        <v>0.019171307012</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2211,25 +2217,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="F33" s="14">
-        <v>420221</v>
+        <v>154814</v>
       </c>
       <c r="G33" s="15">
-        <v>2156.57</v>
+        <v>2903.38</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0178057827563</v>
+        <v>0.019163188639</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2240,25 +2246,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F34" s="14">
-        <v>995837</v>
+        <v>414427</v>
       </c>
       <c r="G34" s="15">
-        <v>2125.02</v>
+        <v>2845.87</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0175452892662</v>
+        <v>0.0187836051953</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2269,25 +2275,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="F35" s="14">
-        <v>135145</v>
+        <v>509314</v>
       </c>
       <c r="G35" s="15">
-        <v>2116.64</v>
+        <v>2769.65</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0174760995532</v>
+        <v>0.0182805300766</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2298,25 +2304,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="F36" s="14">
-        <v>7186</v>
+        <v>180803</v>
       </c>
       <c r="G36" s="15">
-        <v>1997.41</v>
+        <v>2577.35</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0164916735999</v>
+        <v>0.0170112917491</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2336,16 +2342,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F37" s="14">
-        <v>1840660</v>
+        <v>8653</v>
       </c>
       <c r="G37" s="15">
-        <v>1862.75</v>
+        <v>2560.86</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0153798494041</v>
+        <v>0.0169024527475</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2356,25 +2362,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F38" s="14">
-        <v>358741</v>
+        <v>2186043</v>
       </c>
       <c r="G38" s="15">
-        <v>1839.62</v>
+        <v>2508.7</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0151888758882</v>
+        <v>0.0165581809266</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2385,25 +2391,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="F39" s="14">
-        <v>148838</v>
+        <v>163251</v>
       </c>
       <c r="G39" s="15">
-        <v>1792.75</v>
+        <v>2492.84</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0148018923737</v>
+        <v>0.016453500116</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2414,25 +2420,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F40" s="14">
-        <v>1799768</v>
+        <v>431123</v>
       </c>
       <c r="G40" s="15">
-        <v>1678.64</v>
+        <v>2386.27</v>
       </c>
       <c r="H40" s="16">
-        <v>0.013859739849</v>
+        <v>0.0157501057917</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2443,25 +2449,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F41" s="14">
-        <v>315663</v>
+        <v>2235713</v>
       </c>
       <c r="G41" s="15">
-        <v>1672.54</v>
+        <v>2365.83</v>
       </c>
       <c r="H41" s="16">
-        <v>0.013809375022</v>
+        <v>0.0156151955919</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2472,25 +2478,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F42" s="14">
-        <v>27993</v>
+        <v>245848</v>
       </c>
       <c r="G42" s="15">
-        <v>1644.49</v>
+        <v>2332.85</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0135777793834</v>
+        <v>0.0153975175886</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2501,25 +2507,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F43" s="14">
-        <v>50196</v>
+        <v>67797</v>
       </c>
       <c r="G43" s="15">
-        <v>1640.96</v>
+        <v>2152.35</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0135486338361</v>
+        <v>0.0142061628402</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2530,25 +2536,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F44" s="14">
-        <v>163641</v>
+        <v>234881</v>
       </c>
       <c r="G44" s="15">
-        <v>1632.40</v>
+        <v>2036.89</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0134779579478</v>
+        <v>0.0134440918195</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2559,25 +2565,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="F45" s="14">
-        <v>202841</v>
+        <v>33956</v>
       </c>
       <c r="G45" s="15">
-        <v>1605.59</v>
+        <v>2027.51</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0132566004051</v>
+        <v>0.0133821809744</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2588,25 +2594,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F46" s="14">
-        <v>285275</v>
+        <v>198928</v>
       </c>
       <c r="G46" s="15">
-        <v>1450.91</v>
+        <v>2017.83</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0119794804986</v>
+        <v>0.0133182900383</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2617,25 +2623,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="F47" s="14">
-        <v>193236</v>
+        <v>57306</v>
       </c>
       <c r="G47" s="15">
-        <v>1446.08</v>
+        <v>1871.38</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0119396014636</v>
+        <v>0.0123516756178</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2646,25 +2652,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="F48" s="14">
-        <v>953969</v>
+        <v>382568</v>
       </c>
       <c r="G48" s="15">
-        <v>1439.92</v>
+        <v>1847.61</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0118887412449</v>
+        <v>0.012194786408</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2675,25 +2681,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="F49" s="14">
-        <v>686183</v>
+        <v>5609</v>
       </c>
       <c r="G49" s="15">
-        <v>1427.88</v>
+        <v>1762.07</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0117893326357</v>
+        <v>0.0116301964624</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2704,25 +2710,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F50" s="14">
-        <v>1689444</v>
+        <v>346702</v>
       </c>
       <c r="G50" s="15">
-        <v>1360.85</v>
+        <v>1691.73</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0112358974965</v>
+        <v>0.0111659311272</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2733,25 +2739,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F51" s="14">
-        <v>4629</v>
+        <v>253810</v>
       </c>
       <c r="G51" s="15">
-        <v>1329.87</v>
+        <v>1681.24</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0109801102279</v>
+        <v>0.0110966939454</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2762,25 +2768,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="F52" s="14">
-        <v>161041</v>
+        <v>1158692</v>
       </c>
       <c r="G52" s="15">
-        <v>1324.24</v>
+        <v>1610</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0109336259696</v>
+        <v>0.0106264883373</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2791,25 +2797,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F53" s="14">
-        <v>133617</v>
+        <v>162116</v>
       </c>
       <c r="G53" s="15">
-        <v>1296.42</v>
+        <v>1507.68</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0107039293327</v>
+        <v>0.0099511453021</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2820,25 +2826,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F54" s="14">
-        <v>208476</v>
+        <v>78498</v>
       </c>
       <c r="G54" s="15">
-        <v>1284.21</v>
+        <v>1450.02</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0106031171135</v>
+        <v>0.0095705718129</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2849,25 +2855,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F55" s="14">
-        <v>1031501</v>
+        <v>144108</v>
       </c>
       <c r="G55" s="15">
-        <v>1191.28</v>
+        <v>1375.44</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0098358378731</v>
+        <v>0.0090783211917</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -2878,25 +2884,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="F56" s="14">
-        <v>118511</v>
+        <v>53902</v>
       </c>
       <c r="G56" s="15">
-        <v>1001.95</v>
+        <v>1335.77</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0082726292365</v>
+        <v>0.0088164871592</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -2907,25 +2913,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F57" s="14">
-        <v>148033</v>
+        <v>251626</v>
       </c>
       <c r="G57" s="15">
-        <v>952</v>
+        <v>838.04</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0078602156127</v>
+        <v>0.0055313181901</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -2936,6 +2942,27 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" s="14">
+        <v>603365</v>
+      </c>
+      <c r="G58" s="15">
+        <v>736.11</v>
+      </c>
+      <c r="H58" s="16">
+        <v>0.0048585492732</v>
+      </c>
+      <c r="I58" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J58" s="11" t="s">
@@ -2943,28 +2970,7 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I59" s="9" t="s">
+      <c r="B59" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J59" s="11" t="s">
@@ -2972,7 +2978,28 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I60" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J60" s="11" t="s">
@@ -2980,28 +3007,7 @@
       </c>
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
-      <c r="B61" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I61" s="9" t="s">
+      <c r="B61" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J61" s="11" t="s">
@@ -3009,7 +3015,28 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I62" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J62" s="11" t="s">
@@ -3017,36 +3044,36 @@
       </c>
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" ht="15" customHeight="1">
-      <c r="B64" s="12" t="s">
+      <c r="C64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I64" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J64" s="11" t="s">
@@ -3054,28 +3081,7 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I65" s="9" t="s">
+      <c r="B65" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J65" s="11" t="s">
@@ -3083,7 +3089,28 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I66" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J66" s="11" t="s">
@@ -3091,36 +3118,36 @@
       </c>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="15" customHeight="1">
+      <c r="B68" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" ht="15" customHeight="1">
-      <c r="B68" s="12" t="s">
+      <c r="H68" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I68" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J68" s="11" t="s">
@@ -3128,28 +3155,7 @@
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
-      <c r="B69" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I69" s="9" t="s">
+      <c r="B69" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J69" s="11" t="s">
@@ -3157,7 +3163,28 @@
       </c>
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I70" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J70" s="11" t="s">
@@ -3165,28 +3192,7 @@
       </c>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
-      <c r="B71" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I71" s="9" t="s">
+      <c r="B71" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J71" s="11" t="s">
@@ -3194,7 +3200,28 @@
       </c>
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I72" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J72" s="11" t="s">
@@ -3202,28 +3229,7 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I73" s="9" t="s">
+      <c r="B73" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J73" s="11" t="s">
@@ -3231,7 +3237,28 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I74" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J74" s="11" t="s">
@@ -3239,28 +3266,7 @@
       </c>
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I75" s="9" t="s">
+      <c r="B75" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J75" s="11" t="s">
@@ -3268,7 +3274,28 @@
       </c>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I76" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J76" s="11" t="s">
@@ -3276,28 +3303,7 @@
       </c>
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I77" s="9" t="s">
+      <c r="B77" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J77" s="11" t="s">
@@ -3305,7 +3311,28 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I78" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J78" s="11" t="s">
@@ -3313,28 +3340,7 @@
       </c>
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I79" s="9" t="s">
+      <c r="B79" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J79" s="11" t="s">
@@ -3342,7 +3348,28 @@
       </c>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I80" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J80" s="11" t="s">
@@ -3350,28 +3377,7 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I81" s="9" t="s">
+      <c r="B81" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J81" s="11" t="s">
@@ -3379,7 +3385,28 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J82" s="11" t="s">
@@ -3387,28 +3414,7 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="I83" s="9" t="s">
+      <c r="B83" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J83" s="11" t="s">
@@ -3416,7 +3422,28 @@
       </c>
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I84" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J84" s="11" t="s">
@@ -3424,28 +3451,7 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9">
-        <v>40.69</v>
-      </c>
-      <c r="H85" s="10">
-        <v>0.0003359581652</v>
-      </c>
-      <c r="I85" s="9" t="s">
+      <c r="B85" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J85" s="11" t="s">
@@ -3453,7 +3459,28 @@
       </c>
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9">
+        <v>222.65</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0.0014695575331</v>
+      </c>
+      <c r="I86" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J86" s="11" t="s">
@@ -3461,37 +3488,16 @@
       </c>
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="18">
-        <v>-23.52954420002061</v>
-      </c>
-      <c r="H87" s="19">
-        <v>-0.00019427236416272783</v>
-      </c>
-      <c r="I87" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="20" t="s">
+      <c r="B87" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C88" s="18" t="s">
         <v>13</v>
@@ -3506,10 +3512,10 @@
         <v>13</v>
       </c>
       <c r="G88" s="18">
-        <v>121116.2704558</v>
+        <v>-107.72132159993635</v>
       </c>
       <c r="H88" s="19">
-        <v>0.999999999997437</v>
+        <v>-0.0007109933960638379</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>13</v>
@@ -3518,157 +3524,170 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="2:3" ht="15" customHeight="1">
-      <c r="B90" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C90" s="22"/>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="18">
+        <v>151508.1886784</v>
+      </c>
+      <c r="H89" s="19">
+        <v>0.9999999999977363</v>
+      </c>
+      <c r="I89" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="20" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="91" spans="2:3" ht="15" customHeight="1">
-      <c r="B91" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C91" s="24" t="s">
+      <c r="B91" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" s="22"/>
+    </row>
+    <row r="92" spans="2:3" ht="15" customHeight="1">
+      <c r="B92" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" s="24" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" ht="15" customHeight="1">
-      <c r="B92" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="C92" s="26">
-        <v>49000</v>
       </c>
     </row>
     <row r="93" spans="2:3" ht="15" customHeight="1">
       <c r="B93" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C93" s="26">
-        <v>81350</v>
+        <v>159</v>
+      </c>
+      <c r="C93" s="25">
+        <v>3000</v>
       </c>
     </row>
     <row r="94" spans="2:3" ht="15" customHeight="1">
       <c r="B94" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="C94" s="26">
-        <v>285000</v>
+        <v>160</v>
+      </c>
+      <c r="C94" s="25">
+        <v>70000</v>
       </c>
     </row>
     <row r="95" spans="2:3" ht="15" customHeight="1">
       <c r="B95" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C95" s="26">
-        <v>220106</v>
+        <v>161</v>
+      </c>
+      <c r="C95" s="25">
+        <v>20000</v>
       </c>
     </row>
     <row r="96" spans="2:3" ht="15" customHeight="1">
       <c r="B96" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C96" s="26">
-        <v>2158</v>
+        <v>162</v>
+      </c>
+      <c r="C96" s="25">
+        <v>2520</v>
       </c>
     </row>
     <row r="97" spans="2:3" ht="15" customHeight="1">
       <c r="B97" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="C97" s="26">
-        <v>21525</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" ht="15" customHeight="1">
-      <c r="B98" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C98" s="26">
-        <v>44300</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9" ht="15" customHeight="1">
+        <v>163</v>
+      </c>
+      <c r="C97" s="25">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" ht="15" customHeight="1">
+      <c r="B99" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C99" s="26"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
+      <c r="H99" s="26"/>
+      <c r="I99" s="26"/>
+    </row>
+    <row r="100" spans="2:8" ht="15" customHeight="1">
       <c r="B100" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C100" s="27"/>
-      <c r="D100" s="27"/>
-      <c r="E100" s="27"/>
-      <c r="F100" s="27"/>
-      <c r="G100" s="27"/>
-      <c r="H100" s="27"/>
-      <c r="I100" s="27"/>
-    </row>
-    <row r="101" spans="2:8" ht="15" customHeight="1">
-      <c r="B101" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C101" s="27"/>
-      <c r="D101" s="27"/>
-      <c r="E101" s="27"/>
-      <c r="F101" s="27"/>
-      <c r="G101" s="27"/>
-      <c r="H101" s="27"/>
+        <v>165</v>
+      </c>
+      <c r="C100" s="26"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
+      <c r="H100" s="26"/>
+    </row>
+    <row r="101" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B101" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C101" s="26"/>
+      <c r="D101" s="26"/>
+      <c r="E101" s="26"/>
+      <c r="F101" s="26"/>
+      <c r="G101" s="26"/>
+      <c r="H101" s="26"/>
     </row>
     <row r="102" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B102" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C102" s="27"/>
-      <c r="D102" s="27"/>
-      <c r="E102" s="27"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="27"/>
-      <c r="H102" s="27"/>
+      <c r="B102" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C102" s="26"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="26"/>
+      <c r="H102" s="26"/>
     </row>
     <row r="103" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B103" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C103" s="27"/>
-      <c r="D103" s="27"/>
-      <c r="E103" s="27"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
-      <c r="H103" s="27"/>
-    </row>
-    <row r="104" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B104" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="C104" s="27"/>
-      <c r="D104" s="27"/>
-      <c r="E104" s="27"/>
-      <c r="F104" s="27"/>
-      <c r="G104" s="27"/>
-      <c r="H104" s="27"/>
-    </row>
-    <row r="107" ht="15">
-      <c r="B107" s="27" t="s">
-        <v>166</v>
+      <c r="B103" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C103" s="26"/>
+      <c r="D103" s="26"/>
+      <c r="E103" s="26"/>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
+      <c r="H103" s="26"/>
+    </row>
+    <row r="106" ht="15">
+      <c r="B106" s="26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="121" ht="15">
+      <c r="B121" s="26" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="122" ht="15">
-      <c r="B122" s="27" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="123" ht="15">
-      <c r="B123" s="27" t="s">
-        <v>168</v>
+      <c r="B122" s="26" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B101:H101"/>
     <mergeCell ref="B102:H102"/>
     <mergeCell ref="B103:H103"/>
-    <mergeCell ref="B104:H104"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B100:I100"/>
-    <mergeCell ref="B101:H101"/>
+    <mergeCell ref="B99:I99"/>
+    <mergeCell ref="B100:H100"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
